--- a/Get variables/Data_Dictionary_020923.xlsx
+++ b/Get variables/Data_Dictionary_020923.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/arogusk2_ed_ac_uk/Documents/HELIOS-BD/Side Projects/BioBank Project/Cathy files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arogusk2\OneDrive - University of Edinburgh\HELIOS-BD\Side Projects\BioBank Project\Git\biobank-time-dimensions\Get variables\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Primary demographics" sheetId="2" r:id="rId1"/>
@@ -3013,6 +3013,8 @@
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
